--- a/AAII_Financials/Yearly/IMPJY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IMPJY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>IMPJY</t>
   </si>
@@ -1715,10 +1715,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>11738900</v>
+        <v>12405900</v>
       </c>
       <c r="E43" s="3">
-        <v>10028600</v>
+        <v>10823400</v>
       </c>
       <c r="F43" s="3">
         <v>9757800</v>
@@ -1781,10 +1781,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1000000</v>
+        <v>726800</v>
       </c>
       <c r="E45" s="3">
-        <v>1178600</v>
+        <v>829200</v>
       </c>
       <c r="F45" s="3">
         <v>922500</v>
@@ -1847,10 +1847,10 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>898200</v>
+        <v>882300</v>
       </c>
       <c r="E47" s="3">
-        <v>806200</v>
+        <v>792300</v>
       </c>
       <c r="F47" s="3">
         <v>734700</v>
@@ -2011,11 +2011,11 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>8</v>
+      <c r="D52" s="3">
+        <v>95800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>105900</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>8</v>
